--- a/data/master_items.xlsx
+++ b/data/master_items.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VytalGuard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42DEE65-A5A1-4F49-BA79-84BEBEBDBCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508A528A-B78F-4573-9C19-F05D7551155B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="3615" windowWidth="25860" windowHeight="13020" xr2:uid="{F48D9600-22DC-4A3D-A084-2812DC8ADD7C}"/>
+    <workbookView xWindow="3525" yWindow="0" windowWidth="26985" windowHeight="21000" xr2:uid="{F48D9600-22DC-4A3D-A084-2812DC8ADD7C}"/>
   </bookViews>
   <sheets>
     <sheet name="master" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">master!$A$1:$W$382</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2792,16 +2795,16 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -2811,10 +2814,10 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C3" t="s">
         <v>257</v>
@@ -2830,16 +2833,16 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2849,10 +2852,10 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>264</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
         <v>257</v>
@@ -2868,10 +2871,10 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>267</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
         <v>257</v>
@@ -2887,16 +2890,16 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -2906,10 +2909,10 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
         <v>257</v>
@@ -2925,16 +2928,16 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -2944,10 +2947,10 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C10" t="s">
         <v>257</v>
@@ -2963,10 +2966,10 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
         <v>257</v>
@@ -2982,10 +2985,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
         <v>257</v>
@@ -3001,10 +3004,10 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C13" t="s">
         <v>257</v>
@@ -3020,10 +3023,10 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C14" t="s">
         <v>257</v>
@@ -3039,10 +3042,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
         <v>257</v>
@@ -3058,10 +3061,10 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C16" t="s">
         <v>257</v>
@@ -3077,10 +3080,10 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C17" t="s">
         <v>257</v>
@@ -3096,10 +3099,10 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C18" t="s">
         <v>257</v>
@@ -3115,10 +3118,10 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C19" t="s">
         <v>257</v>
@@ -3134,10 +3137,10 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
         <v>257</v>
@@ -3153,10 +3156,10 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s">
         <v>257</v>
@@ -3172,10 +3175,10 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
         <v>257</v>
@@ -3191,10 +3194,10 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>285</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
         <v>257</v>
@@ -3210,10 +3213,10 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s">
         <v>257</v>
@@ -3229,10 +3232,10 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="B25" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="C25" t="s">
         <v>257</v>
@@ -3248,10 +3251,10 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C26" t="s">
         <v>257</v>
@@ -3267,10 +3270,10 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C27" t="s">
         <v>257</v>
@@ -3286,10 +3289,10 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>237</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C28" t="s">
         <v>257</v>
@@ -3305,16 +3308,16 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C29" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -3324,16 +3327,16 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C30" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -3343,16 +3346,16 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -3362,16 +3365,16 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -3381,16 +3384,16 @@
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>301</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C33" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
@@ -3400,16 +3403,16 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="B34" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C34" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -3419,10 +3422,10 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C35" t="s">
         <v>257</v>
@@ -3438,10 +3441,10 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>307</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C36" t="s">
         <v>257</v>
@@ -3457,16 +3460,16 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="C37" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D37" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
         <v>5</v>
@@ -3476,10 +3479,10 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>311</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="C38" t="s">
         <v>257</v>
@@ -3495,10 +3498,10 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="C39" t="s">
         <v>257</v>
@@ -3514,10 +3517,10 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>245</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="C40" t="s">
         <v>257</v>
@@ -3533,10 +3536,10 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>315</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C41" t="s">
         <v>257</v>
@@ -3552,10 +3555,10 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>317</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C42" t="s">
         <v>257</v>
@@ -3571,10 +3574,10 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C43" t="s">
         <v>257</v>
@@ -3590,10 +3593,10 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C44" t="s">
         <v>257</v>
@@ -3609,10 +3612,10 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C45" t="s">
         <v>257</v>
@@ -3628,10 +3631,10 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C46" t="s">
         <v>257</v>
@@ -3647,10 +3650,10 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B47" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C47" t="s">
         <v>257</v>
@@ -3666,10 +3669,10 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C48" t="s">
         <v>257</v>
@@ -3685,16 +3688,16 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E49" t="s">
         <v>5</v>
@@ -3704,10 +3707,10 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C50" t="s">
         <v>257</v>
@@ -3723,10 +3726,10 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C51" t="s">
         <v>257</v>
@@ -3742,10 +3745,10 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C52" t="s">
         <v>257</v>
@@ -3761,10 +3764,10 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="C53" t="s">
         <v>257</v>
@@ -3780,10 +3783,10 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B54" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C54" t="s">
         <v>257</v>
@@ -3799,10 +3802,10 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>333</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="C55" t="s">
         <v>257</v>
@@ -3818,10 +3821,10 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>335</v>
+        <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="C56" t="s">
         <v>257</v>
@@ -3837,10 +3840,10 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C57" t="s">
         <v>257</v>
@@ -3856,10 +3859,10 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>338</v>
+        <v>172</v>
       </c>
       <c r="B58" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C58" t="s">
         <v>257</v>
@@ -3875,10 +3878,10 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C59" t="s">
         <v>257</v>
@@ -3894,10 +3897,10 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C60" t="s">
         <v>257</v>
@@ -3913,16 +3916,16 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
         <v>5</v>
@@ -3932,16 +3935,16 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>343</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
         <v>5</v>
@@ -3951,16 +3954,16 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D63" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E63" t="s">
         <v>5</v>
@@ -3970,16 +3973,16 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="B64" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E64" t="s">
         <v>5</v>
@@ -3989,10 +3992,10 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C65" t="s">
         <v>257</v>
@@ -4008,10 +4011,10 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="B66" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C66" t="s">
         <v>257</v>
@@ -4027,10 +4030,10 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C67" t="s">
         <v>257</v>
@@ -4046,10 +4049,10 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>373</v>
       </c>
       <c r="B68" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C68" t="s">
         <v>257</v>
@@ -4065,10 +4068,10 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>212</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C69" t="s">
         <v>257</v>
@@ -4084,10 +4087,10 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C70" t="s">
         <v>257</v>
@@ -4103,10 +4106,10 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C71" t="s">
         <v>257</v>
@@ -4122,16 +4125,16 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C72" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E72" t="s">
         <v>5</v>
@@ -4141,10 +4144,10 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="B73" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C73" t="s">
         <v>257</v>
@@ -4160,10 +4163,10 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="B74" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C74" t="s">
         <v>257</v>
@@ -4179,10 +4182,10 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="B75" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="C75" t="s">
         <v>257</v>
@@ -4198,10 +4201,10 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C76" t="s">
         <v>257</v>
@@ -4217,10 +4220,10 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C77" t="s">
         <v>257</v>
@@ -4236,10 +4239,10 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>247</v>
       </c>
       <c r="B78" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C78" t="s">
         <v>257</v>
@@ -4255,16 +4258,16 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>363</v>
+        <v>175</v>
       </c>
       <c r="B79" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E79" t="s">
         <v>5</v>
@@ -4274,10 +4277,10 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C80" t="s">
         <v>257</v>
@@ -4293,16 +4296,16 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C81" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D81" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" t="s">
         <v>5</v>
@@ -4312,10 +4315,10 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C82" t="s">
         <v>257</v>
@@ -4331,10 +4334,10 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C83" t="s">
         <v>257</v>
@@ -4350,10 +4353,10 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>113</v>
+        <v>392</v>
       </c>
       <c r="B84" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C84" t="s">
         <v>257</v>
@@ -4369,10 +4372,10 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C85" t="s">
         <v>257</v>
@@ -4388,10 +4391,10 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>233</v>
+        <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C86" t="s">
         <v>257</v>
@@ -4407,10 +4410,10 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="B87" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C87" t="s">
         <v>257</v>
@@ -4426,16 +4429,16 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="C88" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D88" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E88" t="s">
         <v>5</v>
@@ -4445,10 +4448,10 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C89" t="s">
         <v>257</v>
@@ -4464,10 +4467,10 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="B90" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="C90" t="s">
         <v>257</v>
@@ -4483,10 +4486,10 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>224</v>
+        <v>408</v>
       </c>
       <c r="B91" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="C91" t="s">
         <v>257</v>
@@ -4502,10 +4505,10 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>248</v>
+        <v>410</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="C92" t="s">
         <v>257</v>
@@ -4521,10 +4524,10 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="B93" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="C93" t="s">
         <v>257</v>
@@ -4540,10 +4543,10 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="C94" t="s">
         <v>257</v>
@@ -4559,10 +4562,10 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="C95" t="s">
         <v>257</v>
@@ -4578,10 +4581,10 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B96" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="C96" t="s">
         <v>257</v>
@@ -4597,10 +4600,10 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
         <v>257</v>
@@ -4616,10 +4619,10 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>247</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="C98" t="s">
         <v>257</v>
@@ -4635,10 +4638,10 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>175</v>
+        <v>419</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="C99" t="s">
         <v>257</v>
@@ -4654,10 +4657,10 @@
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="C100" t="s">
         <v>257</v>
@@ -4673,10 +4676,10 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="C101" t="s">
         <v>257</v>
@@ -4692,10 +4695,10 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="C102" t="s">
         <v>257</v>
@@ -4711,10 +4714,10 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="C103" t="s">
         <v>257</v>
@@ -4730,10 +4733,10 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>392</v>
+        <v>242</v>
       </c>
       <c r="B104" t="s">
-        <v>393</v>
+        <v>435</v>
       </c>
       <c r="C104" t="s">
         <v>257</v>
@@ -4749,16 +4752,16 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="B105" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D105" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E105" t="s">
         <v>5</v>
@@ -4768,10 +4771,10 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="B106" t="s">
-        <v>396</v>
+        <v>443</v>
       </c>
       <c r="C106" t="s">
         <v>257</v>
@@ -4787,16 +4790,16 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="B107" t="s">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="C107" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E107" t="s">
         <v>5</v>
@@ -4806,10 +4809,10 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>39</v>
+        <v>447</v>
       </c>
       <c r="B108" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
       <c r="C108" t="s">
         <v>257</v>
@@ -4825,10 +4828,10 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="B109" t="s">
-        <v>401</v>
+        <v>450</v>
       </c>
       <c r="C109" t="s">
         <v>257</v>
@@ -4844,16 +4847,16 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="B110" t="s">
-        <v>402</v>
+        <v>451</v>
       </c>
       <c r="C110" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E110" t="s">
         <v>5</v>
@@ -4863,16 +4866,16 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="C111" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D111" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E111" t="s">
         <v>5</v>
@@ -4882,10 +4885,10 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>404</v>
+        <v>136</v>
       </c>
       <c r="B112" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="C112" t="s">
         <v>257</v>
@@ -4901,10 +4904,10 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="B113" t="s">
-        <v>406</v>
+        <v>455</v>
       </c>
       <c r="C113" t="s">
         <v>257</v>
@@ -4920,10 +4923,10 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>232</v>
+        <v>456</v>
       </c>
       <c r="B114" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="C114" t="s">
         <v>257</v>
@@ -4939,10 +4942,10 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="B115" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="C115" t="s">
         <v>257</v>
@@ -4958,10 +4961,10 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="B116" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
       <c r="C116" t="s">
         <v>257</v>
@@ -4977,10 +4980,10 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>412</v>
+        <v>19</v>
       </c>
       <c r="B117" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="C117" t="s">
         <v>257</v>
@@ -4996,10 +4999,10 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="B118" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C118" t="s">
         <v>257</v>
@@ -5015,10 +5018,10 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="B119" t="s">
-        <v>415</v>
+        <v>464</v>
       </c>
       <c r="C119" t="s">
         <v>257</v>
@@ -5034,10 +5037,10 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B120" t="s">
-        <v>416</v>
+        <v>471</v>
       </c>
       <c r="C120" t="s">
         <v>257</v>
@@ -5053,10 +5056,10 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="B121" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="C121" t="s">
         <v>257</v>
@@ -5072,10 +5075,10 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="B122" t="s">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="C122" t="s">
         <v>257</v>
@@ -5091,10 +5094,10 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="B123" t="s">
-        <v>420</v>
+        <v>476</v>
       </c>
       <c r="C123" t="s">
         <v>257</v>
@@ -5110,10 +5113,10 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B124" t="s">
-        <v>421</v>
+        <v>477</v>
       </c>
       <c r="C124" t="s">
         <v>257</v>
@@ -5129,16 +5132,16 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>422</v>
+        <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="C125" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D125" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E125" t="s">
         <v>5</v>
@@ -5148,16 +5151,16 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>424</v>
+        <v>29</v>
       </c>
       <c r="B126" t="s">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="C126" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D126" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126" t="s">
         <v>5</v>
@@ -5167,10 +5170,10 @@
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B127" t="s">
-        <v>426</v>
+        <v>495</v>
       </c>
       <c r="C127" t="s">
         <v>257</v>
@@ -5186,16 +5189,16 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>427</v>
+        <v>150</v>
       </c>
       <c r="B128" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="C128" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D128" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E128" t="s">
         <v>5</v>
@@ -5205,16 +5208,16 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>429</v>
+        <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>430</v>
+        <v>497</v>
       </c>
       <c r="C129" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D129" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E129" t="s">
         <v>5</v>
@@ -5224,16 +5227,16 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>431</v>
+        <v>498</v>
       </c>
       <c r="C130" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E130" t="s">
         <v>5</v>
@@ -5243,16 +5246,16 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="B131" t="s">
-        <v>432</v>
+        <v>499</v>
       </c>
       <c r="C131" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D131" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E131" t="s">
         <v>5</v>
@@ -5262,10 +5265,10 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="B132" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="C132" t="s">
         <v>257</v>
@@ -5281,10 +5284,10 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="B133" t="s">
-        <v>434</v>
+        <v>501</v>
       </c>
       <c r="C133" t="s">
         <v>257</v>
@@ -5300,10 +5303,10 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B134" t="s">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="C134" t="s">
         <v>257</v>
@@ -5319,10 +5322,10 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B135" t="s">
-        <v>436</v>
+        <v>511</v>
       </c>
       <c r="C135" t="s">
         <v>257</v>
@@ -5338,16 +5341,16 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="B136" t="s">
-        <v>438</v>
+        <v>512</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D136" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E136" t="s">
         <v>5</v>
@@ -5357,16 +5360,16 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>439</v>
+        <v>221</v>
       </c>
       <c r="B137" t="s">
-        <v>440</v>
+        <v>513</v>
       </c>
       <c r="C137" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D137" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E137" t="s">
         <v>5</v>
@@ -5376,16 +5379,16 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>225</v>
+        <v>37</v>
       </c>
       <c r="B138" t="s">
-        <v>441</v>
+        <v>515</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D138" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E138" t="s">
         <v>5</v>
@@ -5395,10 +5398,10 @@
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>442</v>
+        <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>443</v>
+        <v>516</v>
       </c>
       <c r="C139" t="s">
         <v>257</v>
@@ -5414,16 +5417,16 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B140" t="s">
-        <v>444</v>
+        <v>517</v>
       </c>
       <c r="C140" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D140" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E140" t="s">
         <v>5</v>
@@ -5433,10 +5436,10 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>445</v>
+        <v>520</v>
       </c>
       <c r="B141" t="s">
-        <v>446</v>
+        <v>521</v>
       </c>
       <c r="C141" t="s">
         <v>257</v>
@@ -5452,10 +5455,10 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>447</v>
+        <v>210</v>
       </c>
       <c r="B142" t="s">
-        <v>448</v>
+        <v>522</v>
       </c>
       <c r="C142" t="s">
         <v>257</v>
@@ -5471,10 +5474,10 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>449</v>
+        <v>104</v>
       </c>
       <c r="B143" t="s">
-        <v>450</v>
+        <v>523</v>
       </c>
       <c r="C143" t="s">
         <v>257</v>
@@ -5490,10 +5493,10 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B144" t="s">
-        <v>451</v>
+        <v>525</v>
       </c>
       <c r="C144" t="s">
         <v>257</v>
@@ -5509,10 +5512,10 @@
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="B145" t="s">
-        <v>452</v>
+        <v>526</v>
       </c>
       <c r="C145" t="s">
         <v>257</v>
@@ -5528,10 +5531,10 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="B146" t="s">
-        <v>453</v>
+        <v>527</v>
       </c>
       <c r="C146" t="s">
         <v>257</v>
@@ -5547,16 +5550,16 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B147" t="s">
-        <v>454</v>
+        <v>528</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E147" t="s">
         <v>5</v>
@@ -5566,10 +5569,10 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B148" t="s">
-        <v>455</v>
+        <v>533</v>
       </c>
       <c r="C148" t="s">
         <v>257</v>
@@ -5585,10 +5588,10 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>456</v>
+        <v>71</v>
       </c>
       <c r="B149" t="s">
-        <v>457</v>
+        <v>534</v>
       </c>
       <c r="C149" t="s">
         <v>257</v>
@@ -5604,10 +5607,10 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>458</v>
+        <v>249</v>
       </c>
       <c r="B150" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
       <c r="C150" t="s">
         <v>257</v>
@@ -5623,10 +5626,10 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="B151" t="s">
-        <v>460</v>
+        <v>542</v>
       </c>
       <c r="C151" t="s">
         <v>257</v>
@@ -5642,10 +5645,10 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="C152" t="s">
         <v>257</v>
@@ -5661,10 +5664,10 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="B153" t="s">
-        <v>462</v>
+        <v>544</v>
       </c>
       <c r="C153" t="s">
         <v>257</v>
@@ -5680,10 +5683,10 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>463</v>
+        <v>194</v>
       </c>
       <c r="B154" t="s">
-        <v>464</v>
+        <v>545</v>
       </c>
       <c r="C154" t="s">
         <v>257</v>
@@ -5699,16 +5702,16 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>191</v>
+        <v>546</v>
       </c>
       <c r="B155" t="s">
-        <v>465</v>
+        <v>547</v>
       </c>
       <c r="C155" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D155" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E155" t="s">
         <v>5</v>
@@ -5718,16 +5721,16 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>466</v>
+        <v>229</v>
       </c>
       <c r="B156" t="s">
-        <v>467</v>
+        <v>548</v>
       </c>
       <c r="C156" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D156" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E156" t="s">
         <v>5</v>
@@ -5737,16 +5740,16 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>468</v>
+        <v>549</v>
       </c>
       <c r="C157" t="s">
-        <v>469</v>
+        <v>257</v>
       </c>
       <c r="D157" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E157" t="s">
         <v>5</v>
@@ -5756,16 +5759,16 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="B158" t="s">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="C158" t="s">
-        <v>469</v>
+        <v>257</v>
       </c>
       <c r="D158" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E158" t="s">
         <v>5</v>
@@ -5775,10 +5778,10 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="B159" t="s">
-        <v>471</v>
+        <v>551</v>
       </c>
       <c r="C159" t="s">
         <v>257</v>
@@ -5794,10 +5797,10 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>472</v>
+        <v>552</v>
       </c>
       <c r="C160" t="s">
         <v>257</v>
@@ -5813,10 +5816,10 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>473</v>
+        <v>553</v>
       </c>
       <c r="B161" t="s">
-        <v>474</v>
+        <v>554</v>
       </c>
       <c r="C161" t="s">
         <v>257</v>
@@ -5832,10 +5835,10 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>475</v>
+        <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>476</v>
+        <v>555</v>
       </c>
       <c r="C162" t="s">
         <v>257</v>
@@ -5851,10 +5854,10 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>46</v>
+        <v>154</v>
       </c>
       <c r="B163" t="s">
-        <v>477</v>
+        <v>556</v>
       </c>
       <c r="C163" t="s">
         <v>257</v>
@@ -5870,16 +5873,16 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>478</v>
+        <v>81</v>
       </c>
       <c r="B164" t="s">
-        <v>479</v>
+        <v>557</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D164" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E164" t="s">
         <v>5</v>
@@ -5889,16 +5892,16 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B165" t="s">
-        <v>480</v>
+        <v>558</v>
       </c>
       <c r="C165" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D165" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E165" t="s">
         <v>5</v>
@@ -5908,10 +5911,10 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B166" t="s">
-        <v>481</v>
+        <v>559</v>
       </c>
       <c r="C166" t="s">
         <v>257</v>
@@ -5927,16 +5930,16 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>482</v>
+        <v>142</v>
       </c>
       <c r="B167" t="s">
-        <v>483</v>
+        <v>563</v>
       </c>
       <c r="C167" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D167" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E167" t="s">
         <v>5</v>
@@ -5946,16 +5949,16 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>484</v>
+        <v>238</v>
       </c>
       <c r="B168" t="s">
-        <v>485</v>
+        <v>577</v>
       </c>
       <c r="C168" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D168" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E168" t="s">
         <v>5</v>
@@ -5965,16 +5968,16 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>486</v>
+        <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>487</v>
+        <v>578</v>
       </c>
       <c r="C169" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D169" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E169" t="s">
         <v>5</v>
@@ -5984,16 +5987,16 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B170" t="s">
-        <v>488</v>
+        <v>579</v>
       </c>
       <c r="C170" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D170" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E170" t="s">
         <v>5</v>
@@ -6003,16 +6006,16 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>489</v>
+        <v>59</v>
       </c>
       <c r="B171" t="s">
-        <v>490</v>
+        <v>582</v>
       </c>
       <c r="C171" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D171" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" t="s">
         <v>5</v>
@@ -6022,16 +6025,16 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>491</v>
+        <v>67</v>
       </c>
       <c r="B172" t="s">
-        <v>492</v>
+        <v>583</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D172" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E172" t="s">
         <v>5</v>
@@ -6041,16 +6044,16 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="B173" t="s">
-        <v>493</v>
+        <v>584</v>
       </c>
       <c r="C173" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D173" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E173" t="s">
         <v>5</v>
@@ -6060,10 +6063,10 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="B174" t="s">
-        <v>494</v>
+        <v>587</v>
       </c>
       <c r="C174" t="s">
         <v>257</v>
@@ -6079,10 +6082,10 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
       <c r="B175" t="s">
-        <v>495</v>
+        <v>588</v>
       </c>
       <c r="C175" t="s">
         <v>257</v>
@@ -6098,10 +6101,10 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>150</v>
+        <v>589</v>
       </c>
       <c r="B176" t="s">
-        <v>496</v>
+        <v>590</v>
       </c>
       <c r="C176" t="s">
         <v>257</v>
@@ -6117,10 +6120,10 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="B177" t="s">
-        <v>497</v>
+        <v>596</v>
       </c>
       <c r="C177" t="s">
         <v>257</v>
@@ -6136,10 +6139,10 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="B178" t="s">
-        <v>498</v>
+        <v>597</v>
       </c>
       <c r="C178" t="s">
         <v>257</v>
@@ -6155,10 +6158,10 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="B179" t="s">
-        <v>499</v>
+        <v>598</v>
       </c>
       <c r="C179" t="s">
         <v>257</v>
@@ -6174,10 +6177,10 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>65</v>
+        <v>243</v>
       </c>
       <c r="B180" t="s">
-        <v>500</v>
+        <v>601</v>
       </c>
       <c r="C180" t="s">
         <v>257</v>
@@ -6193,10 +6196,10 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="B181" t="s">
-        <v>501</v>
+        <v>605</v>
       </c>
       <c r="C181" t="s">
         <v>257</v>
@@ -6212,10 +6215,10 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>502</v>
+        <v>611</v>
       </c>
       <c r="C182" t="s">
         <v>257</v>
@@ -6231,16 +6234,16 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>503</v>
+        <v>612</v>
       </c>
       <c r="B183" t="s">
-        <v>504</v>
+        <v>613</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D183" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E183" t="s">
         <v>5</v>
@@ -6250,16 +6253,16 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>54</v>
+        <v>614</v>
       </c>
       <c r="B184" t="s">
-        <v>505</v>
+        <v>615</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D184" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E184" t="s">
         <v>5</v>
@@ -6269,16 +6272,16 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>506</v>
+        <v>616</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D185" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E185" t="s">
         <v>5</v>
@@ -6288,16 +6291,16 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="B186" t="s">
-        <v>507</v>
+        <v>617</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D186" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E186" t="s">
         <v>5</v>
@@ -6307,16 +6310,16 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
       <c r="B187" t="s">
-        <v>508</v>
+        <v>618</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D187" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E187" t="s">
         <v>5</v>
@@ -6326,16 +6329,16 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>509</v>
+        <v>40</v>
       </c>
       <c r="B188" t="s">
-        <v>510</v>
+        <v>619</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D188" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E188" t="s">
         <v>5</v>
@@ -6345,10 +6348,10 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="B189" t="s">
-        <v>511</v>
+        <v>620</v>
       </c>
       <c r="C189" t="s">
         <v>257</v>
@@ -6364,10 +6367,10 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>512</v>
+        <v>621</v>
       </c>
       <c r="C190" t="s">
         <v>257</v>
@@ -6383,10 +6386,10 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>221</v>
+        <v>622</v>
       </c>
       <c r="B191" t="s">
-        <v>513</v>
+        <v>623</v>
       </c>
       <c r="C191" t="s">
         <v>257</v>
@@ -6402,16 +6405,16 @@
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="B192" t="s">
-        <v>514</v>
+        <v>626</v>
       </c>
       <c r="C192" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D192" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E192" t="s">
         <v>5</v>
@@ -6421,10 +6424,10 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="B193" t="s">
-        <v>515</v>
+        <v>627</v>
       </c>
       <c r="C193" t="s">
         <v>257</v>
@@ -6440,10 +6443,10 @@
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B194" t="s">
-        <v>516</v>
+        <v>628</v>
       </c>
       <c r="C194" t="s">
         <v>257</v>
@@ -6459,10 +6462,10 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="B195" t="s">
-        <v>517</v>
+        <v>629</v>
       </c>
       <c r="C195" t="s">
         <v>257</v>
@@ -6478,16 +6481,16 @@
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>518</v>
+        <v>72</v>
       </c>
       <c r="B196" t="s">
-        <v>519</v>
+        <v>630</v>
       </c>
       <c r="C196" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E196" t="s">
         <v>5</v>
@@ -6497,10 +6500,10 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>520</v>
+        <v>631</v>
       </c>
       <c r="B197" t="s">
-        <v>521</v>
+        <v>632</v>
       </c>
       <c r="C197" t="s">
         <v>257</v>
@@ -6516,10 +6519,10 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="B198" t="s">
-        <v>522</v>
+        <v>635</v>
       </c>
       <c r="C198" t="s">
         <v>257</v>
@@ -6535,10 +6538,10 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B199" t="s">
-        <v>523</v>
+        <v>636</v>
       </c>
       <c r="C199" t="s">
         <v>257</v>
@@ -6554,16 +6557,16 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="B200" t="s">
-        <v>524</v>
+        <v>637</v>
       </c>
       <c r="C200" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D200" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E200" t="s">
         <v>5</v>
@@ -6573,10 +6576,10 @@
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>211</v>
+        <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>525</v>
+        <v>638</v>
       </c>
       <c r="C201" t="s">
         <v>257</v>
@@ -6592,10 +6595,10 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
       <c r="B202" t="s">
-        <v>526</v>
+        <v>639</v>
       </c>
       <c r="C202" t="s">
         <v>257</v>
@@ -6611,10 +6614,10 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>62</v>
+        <v>640</v>
       </c>
       <c r="B203" t="s">
-        <v>527</v>
+        <v>641</v>
       </c>
       <c r="C203" t="s">
         <v>257</v>
@@ -6630,10 +6633,10 @@
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="B204" t="s">
-        <v>528</v>
+        <v>644</v>
       </c>
       <c r="C204" t="s">
         <v>257</v>
@@ -6649,16 +6652,16 @@
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>155</v>
+        <v>645</v>
       </c>
       <c r="B205" t="s">
-        <v>529</v>
+        <v>646</v>
       </c>
       <c r="C205" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D205" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E205" t="s">
         <v>5</v>
@@ -6668,16 +6671,16 @@
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B206" t="s">
-        <v>530</v>
+        <v>647</v>
       </c>
       <c r="C206" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D206" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E206" t="s">
         <v>5</v>
@@ -6687,16 +6690,16 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>531</v>
+        <v>22</v>
       </c>
       <c r="B207" t="s">
-        <v>532</v>
+        <v>648</v>
       </c>
       <c r="C207" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E207" t="s">
         <v>5</v>
@@ -6706,10 +6709,10 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>533</v>
+        <v>650</v>
       </c>
       <c r="C208" t="s">
         <v>257</v>
@@ -6725,10 +6728,10 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="B209" t="s">
-        <v>534</v>
+        <v>651</v>
       </c>
       <c r="C209" t="s">
         <v>257</v>
@@ -6744,10 +6747,10 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>249</v>
+        <v>652</v>
       </c>
       <c r="B210" t="s">
-        <v>535</v>
+        <v>653</v>
       </c>
       <c r="C210" t="s">
         <v>257</v>
@@ -6763,16 +6766,16 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>536</v>
+        <v>230</v>
       </c>
       <c r="B211" t="s">
-        <v>537</v>
+        <v>654</v>
       </c>
       <c r="C211" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D211" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E211" t="s">
         <v>5</v>
@@ -6782,16 +6785,16 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="B212" t="s">
-        <v>538</v>
+        <v>656</v>
       </c>
       <c r="C212" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D212" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E212" t="s">
         <v>5</v>
@@ -6801,16 +6804,16 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>42</v>
+        <v>657</v>
       </c>
       <c r="B213" t="s">
-        <v>539</v>
+        <v>658</v>
       </c>
       <c r="C213" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D213" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E213" t="s">
         <v>5</v>
@@ -6820,16 +6823,16 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>55</v>
+        <v>659</v>
       </c>
       <c r="B214" t="s">
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="C214" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D214" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E214" t="s">
         <v>5</v>
@@ -6839,16 +6842,16 @@
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>183</v>
+        <v>661</v>
       </c>
       <c r="B215" t="s">
-        <v>541</v>
+        <v>662</v>
       </c>
       <c r="C215" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D215" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E215" t="s">
         <v>5</v>
@@ -6858,10 +6861,10 @@
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="B216" t="s">
-        <v>542</v>
+        <v>663</v>
       </c>
       <c r="C216" t="s">
         <v>257</v>
@@ -6877,10 +6880,10 @@
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="B217" t="s">
-        <v>543</v>
+        <v>664</v>
       </c>
       <c r="C217" t="s">
         <v>257</v>
@@ -6896,10 +6899,10 @@
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>61</v>
+        <v>674</v>
       </c>
       <c r="B218" t="s">
-        <v>544</v>
+        <v>675</v>
       </c>
       <c r="C218" t="s">
         <v>257</v>
@@ -6915,10 +6918,10 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>545</v>
+        <v>680</v>
       </c>
       <c r="C219" t="s">
         <v>257</v>
@@ -6934,10 +6937,10 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>546</v>
+        <v>173</v>
       </c>
       <c r="B220" t="s">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="C220" t="s">
         <v>257</v>
@@ -6953,10 +6956,10 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>229</v>
+        <v>685</v>
       </c>
       <c r="B221" t="s">
-        <v>548</v>
+        <v>686</v>
       </c>
       <c r="C221" t="s">
         <v>257</v>
@@ -6972,10 +6975,10 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>164</v>
+        <v>687</v>
       </c>
       <c r="B222" t="s">
-        <v>549</v>
+        <v>688</v>
       </c>
       <c r="C222" t="s">
         <v>257</v>
@@ -6991,10 +6994,10 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>206</v>
+        <v>689</v>
       </c>
       <c r="B223" t="s">
-        <v>550</v>
+        <v>690</v>
       </c>
       <c r="C223" t="s">
         <v>257</v>
@@ -7010,10 +7013,10 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="B224" t="s">
-        <v>551</v>
+        <v>691</v>
       </c>
       <c r="C224" t="s">
         <v>257</v>
@@ -7029,10 +7032,10 @@
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B225" t="s">
-        <v>552</v>
+        <v>693</v>
       </c>
       <c r="C225" t="s">
         <v>257</v>
@@ -7048,10 +7051,10 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>553</v>
+        <v>203</v>
       </c>
       <c r="B226" t="s">
-        <v>554</v>
+        <v>715</v>
       </c>
       <c r="C226" t="s">
         <v>257</v>
@@ -7067,10 +7070,10 @@
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="B227" t="s">
-        <v>555</v>
+        <v>718</v>
       </c>
       <c r="C227" t="s">
         <v>257</v>
@@ -7086,10 +7089,10 @@
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="B228" t="s">
-        <v>556</v>
+        <v>719</v>
       </c>
       <c r="C228" t="s">
         <v>257</v>
@@ -7105,10 +7108,10 @@
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B229" t="s">
-        <v>557</v>
+        <v>724</v>
       </c>
       <c r="C229" t="s">
         <v>257</v>
@@ -7124,10 +7127,10 @@
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="B230" t="s">
-        <v>558</v>
+        <v>725</v>
       </c>
       <c r="C230" t="s">
         <v>257</v>
@@ -7143,10 +7146,10 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="B231" t="s">
-        <v>559</v>
+        <v>726</v>
       </c>
       <c r="C231" t="s">
         <v>257</v>
@@ -7162,16 +7165,16 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>560</v>
+        <v>220</v>
       </c>
       <c r="B232" t="s">
-        <v>561</v>
+        <v>727</v>
       </c>
       <c r="C232" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="D232" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E232" t="s">
         <v>5</v>
@@ -7181,16 +7184,16 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="B233" t="s">
-        <v>562</v>
+        <v>752</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D233" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E233" t="s">
         <v>5</v>
@@ -7200,10 +7203,10 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>142</v>
+        <v>754</v>
       </c>
       <c r="B234" t="s">
-        <v>563</v>
+        <v>755</v>
       </c>
       <c r="C234" t="s">
         <v>257</v>
@@ -7219,16 +7222,16 @@
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>564</v>
+        <v>110</v>
       </c>
       <c r="B235" t="s">
-        <v>565</v>
+        <v>756</v>
       </c>
       <c r="C235" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D235" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E235" t="s">
         <v>5</v>
@@ -7238,16 +7241,16 @@
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>566</v>
+        <v>757</v>
       </c>
       <c r="B236" t="s">
-        <v>567</v>
+        <v>758</v>
       </c>
       <c r="C236" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D236" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E236" t="s">
         <v>5</v>
@@ -7257,16 +7260,16 @@
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>91</v>
+        <v>759</v>
       </c>
       <c r="B237" t="s">
-        <v>568</v>
+        <v>760</v>
       </c>
       <c r="C237" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D237" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E237" t="s">
         <v>5</v>
@@ -7276,16 +7279,16 @@
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>569</v>
+        <v>761</v>
       </c>
       <c r="B238" t="s">
-        <v>570</v>
+        <v>762</v>
       </c>
       <c r="C238" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D238" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E238" t="s">
         <v>5</v>
@@ -7295,16 +7298,16 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>571</v>
+        <v>763</v>
       </c>
       <c r="B239" t="s">
-        <v>572</v>
+        <v>764</v>
       </c>
       <c r="C239" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D239" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E239" t="s">
         <v>5</v>
@@ -7314,16 +7317,16 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>573</v>
+        <v>131</v>
       </c>
       <c r="B240" t="s">
-        <v>574</v>
+        <v>765</v>
       </c>
       <c r="C240" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D240" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E240" t="s">
         <v>5</v>
@@ -7333,16 +7336,16 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>575</v>
+        <v>114</v>
       </c>
       <c r="B241" t="s">
-        <v>576</v>
+        <v>766</v>
       </c>
       <c r="C241" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D241" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E241" t="s">
         <v>5</v>
@@ -7352,10 +7355,10 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="B242" t="s">
-        <v>577</v>
+        <v>767</v>
       </c>
       <c r="C242" t="s">
         <v>257</v>
@@ -7371,10 +7374,10 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="B243" t="s">
-        <v>578</v>
+        <v>768</v>
       </c>
       <c r="C243" t="s">
         <v>257</v>
@@ -7390,10 +7393,10 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>140</v>
+        <v>769</v>
       </c>
       <c r="B244" t="s">
-        <v>579</v>
+        <v>770</v>
       </c>
       <c r="C244" t="s">
         <v>257</v>
@@ -7409,16 +7412,16 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="B245" t="s">
-        <v>581</v>
+        <v>771</v>
       </c>
       <c r="C245" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D245" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E245" t="s">
         <v>5</v>
@@ -7428,10 +7431,10 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="B246" t="s">
-        <v>582</v>
+        <v>772</v>
       </c>
       <c r="C246" t="s">
         <v>257</v>
@@ -7447,10 +7450,10 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>67</v>
+        <v>777</v>
       </c>
       <c r="B247" t="s">
-        <v>583</v>
+        <v>778</v>
       </c>
       <c r="C247" t="s">
         <v>257</v>
@@ -7466,16 +7469,16 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="B248" t="s">
-        <v>584</v>
+        <v>309</v>
       </c>
       <c r="C248" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D248" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E248" t="s">
         <v>5</v>
@@ -7485,13 +7488,13 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>198</v>
+        <v>58</v>
       </c>
       <c r="B249" t="s">
-        <v>585</v>
+        <v>366</v>
       </c>
       <c r="C249" t="s">
-        <v>586</v>
+        <v>310</v>
       </c>
       <c r="D249" t="s">
         <v>3</v>
@@ -7504,16 +7507,16 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>186</v>
+        <v>424</v>
       </c>
       <c r="B250" t="s">
-        <v>587</v>
+        <v>425</v>
       </c>
       <c r="C250" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D250" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E250" t="s">
         <v>5</v>
@@ -7523,16 +7526,16 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>188</v>
+        <v>439</v>
       </c>
       <c r="B251" t="s">
-        <v>588</v>
+        <v>440</v>
       </c>
       <c r="C251" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D251" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E251" t="s">
         <v>5</v>
@@ -7542,16 +7545,16 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>589</v>
+        <v>489</v>
       </c>
       <c r="B252" t="s">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="C252" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D252" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E252" t="s">
         <v>5</v>
@@ -7561,16 +7564,16 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>591</v>
+        <v>227</v>
       </c>
       <c r="B253" t="s">
-        <v>592</v>
+        <v>524</v>
       </c>
       <c r="C253" t="s">
-        <v>469</v>
+        <v>310</v>
       </c>
       <c r="D253" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E253" t="s">
         <v>5</v>
@@ -7580,16 +7583,16 @@
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>101</v>
+        <v>560</v>
       </c>
       <c r="B254" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="C254" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="D254" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E254" t="s">
         <v>5</v>
@@ -7599,16 +7602,16 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>594</v>
+        <v>198</v>
       </c>
       <c r="B255" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C255" t="s">
-        <v>304</v>
+        <v>586</v>
       </c>
       <c r="D255" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E255" t="s">
         <v>5</v>
@@ -7618,16 +7621,16 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B256" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C256" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D256" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E256" t="s">
         <v>5</v>
@@ -7637,16 +7640,16 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="B257" t="s">
-        <v>597</v>
+        <v>665</v>
       </c>
       <c r="C257" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D257" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E257" t="s">
         <v>5</v>
@@ -7656,16 +7659,16 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="B258" t="s">
-        <v>598</v>
+        <v>776</v>
       </c>
       <c r="C258" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D258" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E258" t="s">
         <v>5</v>
@@ -7675,13 +7678,13 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>599</v>
+        <v>162</v>
       </c>
       <c r="B259" t="s">
-        <v>600</v>
+        <v>254</v>
       </c>
       <c r="C259" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="D259" t="s">
         <v>6</v>
@@ -7694,16 +7697,16 @@
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="B260" t="s">
-        <v>601</v>
+        <v>258</v>
       </c>
       <c r="C260" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D260" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E260" t="s">
         <v>5</v>
@@ -7713,16 +7716,16 @@
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>64</v>
+        <v>262</v>
       </c>
       <c r="B261" t="s">
-        <v>602</v>
+        <v>263</v>
       </c>
       <c r="C261" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="D261" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E261" t="s">
         <v>5</v>
@@ -7732,13 +7735,13 @@
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>603</v>
+        <v>149</v>
       </c>
       <c r="B262" t="s">
-        <v>604</v>
+        <v>266</v>
       </c>
       <c r="C262" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="D262" t="s">
         <v>6</v>
@@ -7751,16 +7754,16 @@
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>88</v>
+        <v>293</v>
       </c>
       <c r="B263" t="s">
-        <v>605</v>
+        <v>294</v>
       </c>
       <c r="C263" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="D263" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E263" t="s">
         <v>5</v>
@@ -7770,13 +7773,13 @@
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>33</v>
+        <v>296</v>
       </c>
       <c r="B264" t="s">
-        <v>606</v>
+        <v>297</v>
       </c>
       <c r="C264" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D264" t="s">
         <v>6</v>
@@ -7789,10 +7792,10 @@
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>607</v>
+        <v>48</v>
       </c>
       <c r="B265" t="s">
-        <v>608</v>
+        <v>299</v>
       </c>
       <c r="C265" t="s">
         <v>295</v>
@@ -7808,10 +7811,10 @@
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>609</v>
+        <v>189</v>
       </c>
       <c r="B266" t="s">
-        <v>610</v>
+        <v>300</v>
       </c>
       <c r="C266" t="s">
         <v>295</v>
@@ -7827,16 +7830,16 @@
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>178</v>
+        <v>301</v>
       </c>
       <c r="B267" t="s">
-        <v>611</v>
+        <v>302</v>
       </c>
       <c r="C267" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="D267" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E267" t="s">
         <v>5</v>
@@ -7846,16 +7849,16 @@
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>612</v>
+        <v>27</v>
       </c>
       <c r="B268" t="s">
-        <v>613</v>
+        <v>303</v>
       </c>
       <c r="C268" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="D268" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E268" t="s">
         <v>5</v>
@@ -7865,16 +7868,16 @@
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>614</v>
+        <v>231</v>
       </c>
       <c r="B269" t="s">
-        <v>615</v>
+        <v>327</v>
       </c>
       <c r="C269" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D269" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E269" t="s">
         <v>5</v>
@@ -7884,16 +7887,16 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B270" t="s">
-        <v>616</v>
+        <v>342</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D270" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E270" t="s">
         <v>5</v>
@@ -7903,16 +7906,16 @@
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="B271" t="s">
-        <v>617</v>
+        <v>344</v>
       </c>
       <c r="C271" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D271" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E271" t="s">
         <v>5</v>
@@ -7922,16 +7925,16 @@
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="B272" t="s">
-        <v>618</v>
+        <v>345</v>
       </c>
       <c r="C272" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D272" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E272" t="s">
         <v>5</v>
@@ -7941,16 +7944,16 @@
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="B273" t="s">
-        <v>619</v>
+        <v>347</v>
       </c>
       <c r="C273" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="D273" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E273" t="s">
         <v>5</v>
@@ -7960,16 +7963,16 @@
     </row>
     <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>222</v>
+        <v>355</v>
       </c>
       <c r="B274" t="s">
-        <v>620</v>
+        <v>356</v>
       </c>
       <c r="C274" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D274" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E274" t="s">
         <v>5</v>
@@ -7979,16 +7982,16 @@
     </row>
     <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>195</v>
+        <v>363</v>
       </c>
       <c r="B275" t="s">
-        <v>621</v>
+        <v>364</v>
       </c>
       <c r="C275" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D275" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>5</v>
@@ -7998,16 +8001,16 @@
     </row>
     <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>622</v>
+        <v>375</v>
       </c>
       <c r="B276" t="s">
-        <v>623</v>
+        <v>376</v>
       </c>
       <c r="C276" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D276" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E276" t="s">
         <v>5</v>
@@ -8017,13 +8020,13 @@
     </row>
     <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>624</v>
+        <v>17</v>
       </c>
       <c r="B277" t="s">
-        <v>625</v>
+        <v>394</v>
       </c>
       <c r="C277" t="s">
-        <v>469</v>
+        <v>255</v>
       </c>
       <c r="D277" t="s">
         <v>6</v>
@@ -8036,16 +8039,16 @@
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>219</v>
+        <v>397</v>
       </c>
       <c r="B278" t="s">
-        <v>626</v>
+        <v>398</v>
       </c>
       <c r="C278" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D278" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" t="s">
         <v>5</v>
@@ -8055,16 +8058,16 @@
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>226</v>
+        <v>94</v>
       </c>
       <c r="B279" t="s">
-        <v>627</v>
+        <v>402</v>
       </c>
       <c r="C279" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="D279" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E279" t="s">
         <v>5</v>
@@ -8074,16 +8077,16 @@
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>45</v>
+        <v>228</v>
       </c>
       <c r="B280" t="s">
-        <v>628</v>
+        <v>403</v>
       </c>
       <c r="C280" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="D280" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E280" t="s">
         <v>5</v>
@@ -8093,16 +8096,16 @@
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>66</v>
+        <v>422</v>
       </c>
       <c r="B281" t="s">
-        <v>629</v>
+        <v>423</v>
       </c>
       <c r="C281" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D281" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E281" t="s">
         <v>5</v>
@@ -8112,16 +8115,16 @@
     </row>
     <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="B282" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="C282" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D282" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E282" t="s">
         <v>5</v>
@@ -8131,16 +8134,16 @@
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>631</v>
+        <v>429</v>
       </c>
       <c r="B283" t="s">
-        <v>632</v>
+        <v>430</v>
       </c>
       <c r="C283" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D283" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E283" t="s">
         <v>5</v>
@@ -8150,13 +8153,13 @@
     </row>
     <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>633</v>
+        <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>634</v>
+        <v>431</v>
       </c>
       <c r="C284" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D284" t="s">
         <v>6</v>
@@ -8169,16 +8172,16 @@
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B285" t="s">
-        <v>635</v>
+        <v>432</v>
       </c>
       <c r="C285" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="D285" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E285" t="s">
         <v>5</v>
@@ -8188,16 +8191,16 @@
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>111</v>
+        <v>437</v>
       </c>
       <c r="B286" t="s">
-        <v>636</v>
+        <v>438</v>
       </c>
       <c r="C286" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D286" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E286" t="s">
         <v>5</v>
@@ -8207,16 +8210,16 @@
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="B287" t="s">
-        <v>637</v>
+        <v>441</v>
       </c>
       <c r="C287" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D287" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E287" t="s">
         <v>5</v>
@@ -8226,16 +8229,16 @@
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B288" t="s">
-        <v>638</v>
+        <v>444</v>
       </c>
       <c r="C288" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D288" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E288" t="s">
         <v>5</v>
@@ -8245,16 +8248,16 @@
     </row>
     <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>187</v>
+        <v>11</v>
       </c>
       <c r="B289" t="s">
-        <v>639</v>
+        <v>454</v>
       </c>
       <c r="C289" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D289" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E289" t="s">
         <v>5</v>
@@ -8264,16 +8267,16 @@
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>640</v>
+        <v>191</v>
       </c>
       <c r="B290" t="s">
-        <v>641</v>
+        <v>465</v>
       </c>
       <c r="C290" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D290" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E290" t="s">
         <v>5</v>
@@ -8283,13 +8286,13 @@
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>642</v>
+        <v>466</v>
       </c>
       <c r="B291" t="s">
-        <v>643</v>
+        <v>467</v>
       </c>
       <c r="C291" t="s">
-        <v>469</v>
+        <v>304</v>
       </c>
       <c r="D291" t="s">
         <v>6</v>
@@ -8302,16 +8305,16 @@
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="B292" t="s">
-        <v>644</v>
+        <v>468</v>
       </c>
       <c r="C292" t="s">
-        <v>257</v>
+        <v>469</v>
       </c>
       <c r="D292" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E292" t="s">
         <v>5</v>
@@ -8321,16 +8324,16 @@
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>645</v>
+        <v>63</v>
       </c>
       <c r="B293" t="s">
-        <v>646</v>
+        <v>470</v>
       </c>
       <c r="C293" t="s">
-        <v>257</v>
+        <v>469</v>
       </c>
       <c r="D293" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E293" t="s">
         <v>5</v>
@@ -8340,16 +8343,16 @@
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>158</v>
+        <v>478</v>
       </c>
       <c r="B294" t="s">
-        <v>647</v>
+        <v>479</v>
       </c>
       <c r="C294" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D294" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E294" t="s">
         <v>5</v>
@@ -8359,16 +8362,16 @@
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="B295" t="s">
-        <v>648</v>
+        <v>480</v>
       </c>
       <c r="C295" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D295" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E295" t="s">
         <v>5</v>
@@ -8378,10 +8381,10 @@
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="B296" t="s">
-        <v>649</v>
+        <v>483</v>
       </c>
       <c r="C296" t="s">
         <v>255</v>
@@ -8397,16 +8400,16 @@
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>20</v>
+        <v>484</v>
       </c>
       <c r="B297" t="s">
-        <v>650</v>
+        <v>485</v>
       </c>
       <c r="C297" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D297" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E297" t="s">
         <v>5</v>
@@ -8416,16 +8419,16 @@
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>205</v>
+        <v>486</v>
       </c>
       <c r="B298" t="s">
-        <v>651</v>
+        <v>487</v>
       </c>
       <c r="C298" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D298" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E298" t="s">
         <v>5</v>
@@ -8435,16 +8438,16 @@
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>652</v>
+        <v>128</v>
       </c>
       <c r="B299" t="s">
-        <v>653</v>
+        <v>488</v>
       </c>
       <c r="C299" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D299" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E299" t="s">
         <v>5</v>
@@ -8454,16 +8457,16 @@
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>230</v>
+        <v>491</v>
       </c>
       <c r="B300" t="s">
-        <v>654</v>
+        <v>492</v>
       </c>
       <c r="C300" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D300" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E300" t="s">
         <v>5</v>
@@ -8473,10 +8476,10 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B301" t="s">
-        <v>655</v>
+        <v>493</v>
       </c>
       <c r="C301" t="s">
         <v>255</v>
@@ -8492,16 +8495,16 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>201</v>
+        <v>503</v>
       </c>
       <c r="B302" t="s">
-        <v>656</v>
+        <v>504</v>
       </c>
       <c r="C302" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D302" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E302" t="s">
         <v>5</v>
@@ -8511,16 +8514,16 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>657</v>
+        <v>54</v>
       </c>
       <c r="B303" t="s">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="C303" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D303" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E303" t="s">
         <v>5</v>
@@ -8530,16 +8533,16 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>659</v>
+        <v>31</v>
       </c>
       <c r="B304" t="s">
-        <v>660</v>
+        <v>506</v>
       </c>
       <c r="C304" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D304" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E304" t="s">
         <v>5</v>
@@ -8549,16 +8552,16 @@
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>661</v>
+        <v>246</v>
       </c>
       <c r="B305" t="s">
-        <v>662</v>
+        <v>507</v>
       </c>
       <c r="C305" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D305" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E305" t="s">
         <v>5</v>
@@ -8568,16 +8571,16 @@
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>208</v>
+        <v>13</v>
       </c>
       <c r="B306" t="s">
-        <v>663</v>
+        <v>508</v>
       </c>
       <c r="C306" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D306" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E306" t="s">
         <v>5</v>
@@ -8587,16 +8590,16 @@
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>69</v>
+        <v>509</v>
       </c>
       <c r="B307" t="s">
-        <v>664</v>
+        <v>510</v>
       </c>
       <c r="C307" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D307" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E307" t="s">
         <v>5</v>
@@ -8606,16 +8609,16 @@
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B308" t="s">
-        <v>665</v>
+        <v>514</v>
       </c>
       <c r="C308" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="D308" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>5</v>
@@ -8625,13 +8628,13 @@
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>666</v>
+        <v>518</v>
       </c>
       <c r="B309" t="s">
-        <v>667</v>
+        <v>519</v>
       </c>
       <c r="C309" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D309" t="s">
         <v>6</v>
@@ -8644,13 +8647,13 @@
     </row>
     <row r="310" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>668</v>
+        <v>155</v>
       </c>
       <c r="B310" t="s">
-        <v>669</v>
+        <v>529</v>
       </c>
       <c r="C310" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D310" t="s">
         <v>6</v>
@@ -8663,10 +8666,10 @@
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>670</v>
+        <v>151</v>
       </c>
       <c r="B311" t="s">
-        <v>671</v>
+        <v>530</v>
       </c>
       <c r="C311" t="s">
         <v>255</v>
@@ -8682,13 +8685,13 @@
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>672</v>
+        <v>531</v>
       </c>
       <c r="B312" t="s">
-        <v>673</v>
+        <v>532</v>
       </c>
       <c r="C312" t="s">
-        <v>469</v>
+        <v>255</v>
       </c>
       <c r="D312" t="s">
         <v>6</v>
@@ -8701,16 +8704,16 @@
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>674</v>
+        <v>536</v>
       </c>
       <c r="B313" t="s">
-        <v>675</v>
+        <v>537</v>
       </c>
       <c r="C313" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="D313" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E313" t="s">
         <v>5</v>
@@ -8720,13 +8723,13 @@
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>676</v>
+        <v>126</v>
       </c>
       <c r="B314" t="s">
-        <v>677</v>
+        <v>538</v>
       </c>
       <c r="C314" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="D314" t="s">
         <v>6</v>
@@ -8739,13 +8742,13 @@
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>678</v>
+        <v>42</v>
       </c>
       <c r="B315" t="s">
-        <v>679</v>
+        <v>539</v>
       </c>
       <c r="C315" t="s">
-        <v>469</v>
+        <v>298</v>
       </c>
       <c r="D315" t="s">
         <v>6</v>
@@ -8758,16 +8761,16 @@
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="B316" t="s">
-        <v>680</v>
+        <v>540</v>
       </c>
       <c r="C316" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="D316" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E316" t="s">
         <v>5</v>
@@ -8777,13 +8780,13 @@
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="B317" t="s">
-        <v>681</v>
+        <v>541</v>
       </c>
       <c r="C317" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="D317" t="s">
         <v>6</v>
@@ -8796,13 +8799,13 @@
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>682</v>
+        <v>209</v>
       </c>
       <c r="B318" t="s">
-        <v>683</v>
+        <v>562</v>
       </c>
       <c r="C318" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D318" t="s">
         <v>6</v>
@@ -8815,16 +8818,16 @@
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>173</v>
+        <v>564</v>
       </c>
       <c r="B319" t="s">
-        <v>684</v>
+        <v>565</v>
       </c>
       <c r="C319" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D319" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E319" t="s">
         <v>5</v>
@@ -8834,16 +8837,16 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>685</v>
+        <v>566</v>
       </c>
       <c r="B320" t="s">
-        <v>686</v>
+        <v>567</v>
       </c>
       <c r="C320" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D320" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E320" t="s">
         <v>5</v>
@@ -8853,16 +8856,16 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>687</v>
+        <v>91</v>
       </c>
       <c r="B321" t="s">
-        <v>688</v>
+        <v>568</v>
       </c>
       <c r="C321" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D321" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E321" t="s">
         <v>5</v>
@@ -8872,16 +8875,16 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>689</v>
+        <v>569</v>
       </c>
       <c r="B322" t="s">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="C322" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D322" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>5</v>
@@ -8891,16 +8894,16 @@
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>83</v>
+        <v>571</v>
       </c>
       <c r="B323" t="s">
-        <v>691</v>
+        <v>572</v>
       </c>
       <c r="C323" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D323" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>5</v>
@@ -8910,10 +8913,10 @@
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>7</v>
+        <v>573</v>
       </c>
       <c r="B324" t="s">
-        <v>692</v>
+        <v>574</v>
       </c>
       <c r="C324" t="s">
         <v>259</v>
@@ -8929,16 +8932,16 @@
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>144</v>
+        <v>575</v>
       </c>
       <c r="B325" t="s">
-        <v>693</v>
+        <v>576</v>
       </c>
       <c r="C325" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D325" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E325" t="s">
         <v>5</v>
@@ -8948,13 +8951,13 @@
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>53</v>
+        <v>580</v>
       </c>
       <c r="B326" t="s">
-        <v>694</v>
+        <v>581</v>
       </c>
       <c r="C326" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D326" t="s">
         <v>6</v>
@@ -8967,13 +8970,13 @@
     </row>
     <row r="327" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="B327" t="s">
-        <v>695</v>
+        <v>592</v>
       </c>
       <c r="C327" t="s">
-        <v>259</v>
+        <v>469</v>
       </c>
       <c r="D327" t="s">
         <v>6</v>
@@ -8986,10 +8989,10 @@
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B328" t="s">
-        <v>696</v>
+        <v>593</v>
       </c>
       <c r="C328" t="s">
         <v>255</v>
@@ -9005,13 +9008,13 @@
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>100</v>
+        <v>594</v>
       </c>
       <c r="B329" t="s">
-        <v>697</v>
+        <v>595</v>
       </c>
       <c r="C329" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D329" t="s">
         <v>6</v>
@@ -9024,13 +9027,13 @@
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>698</v>
+        <v>599</v>
       </c>
       <c r="B330" t="s">
-        <v>699</v>
+        <v>600</v>
       </c>
       <c r="C330" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="D330" t="s">
         <v>6</v>
@@ -9043,13 +9046,13 @@
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>161</v>
+        <v>603</v>
       </c>
       <c r="B331" t="s">
-        <v>700</v>
+        <v>604</v>
       </c>
       <c r="C331" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D331" t="s">
         <v>6</v>
@@ -9062,13 +9065,13 @@
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>701</v>
+        <v>33</v>
       </c>
       <c r="B332" t="s">
-        <v>702</v>
+        <v>606</v>
       </c>
       <c r="C332" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D332" t="s">
         <v>6</v>
@@ -9081,13 +9084,13 @@
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>703</v>
+        <v>607</v>
       </c>
       <c r="B333" t="s">
-        <v>704</v>
+        <v>608</v>
       </c>
       <c r="C333" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D333" t="s">
         <v>6</v>
@@ -9100,13 +9103,13 @@
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>705</v>
+        <v>609</v>
       </c>
       <c r="B334" t="s">
-        <v>706</v>
+        <v>610</v>
       </c>
       <c r="C334" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D334" t="s">
         <v>6</v>
@@ -9119,13 +9122,13 @@
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>707</v>
+        <v>624</v>
       </c>
       <c r="B335" t="s">
-        <v>708</v>
+        <v>625</v>
       </c>
       <c r="C335" t="s">
-        <v>259</v>
+        <v>469</v>
       </c>
       <c r="D335" t="s">
         <v>6</v>
@@ -9138,13 +9141,13 @@
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>709</v>
+        <v>633</v>
       </c>
       <c r="B336" t="s">
-        <v>710</v>
+        <v>634</v>
       </c>
       <c r="C336" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D336" t="s">
         <v>6</v>
@@ -9157,13 +9160,13 @@
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>711</v>
+        <v>642</v>
       </c>
       <c r="B337" t="s">
-        <v>712</v>
+        <v>643</v>
       </c>
       <c r="C337" t="s">
-        <v>259</v>
+        <v>469</v>
       </c>
       <c r="D337" t="s">
         <v>6</v>
@@ -9176,13 +9179,13 @@
     </row>
     <row r="338" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>713</v>
+        <v>196</v>
       </c>
       <c r="B338" t="s">
-        <v>714</v>
+        <v>649</v>
       </c>
       <c r="C338" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D338" t="s">
         <v>6</v>
@@ -9195,16 +9198,16 @@
     </row>
     <row r="339" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>203</v>
+        <v>43</v>
       </c>
       <c r="B339" t="s">
-        <v>715</v>
+        <v>655</v>
       </c>
       <c r="C339" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D339" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E339" t="s">
         <v>5</v>
@@ -9214,13 +9217,13 @@
     </row>
     <row r="340" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>716</v>
+        <v>666</v>
       </c>
       <c r="B340" t="s">
-        <v>717</v>
+        <v>667</v>
       </c>
       <c r="C340" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D340" t="s">
         <v>6</v>
@@ -9233,16 +9236,16 @@
     </row>
     <row r="341" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>184</v>
+        <v>668</v>
       </c>
       <c r="B341" t="s">
-        <v>718</v>
+        <v>669</v>
       </c>
       <c r="C341" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D341" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E341" t="s">
         <v>5</v>
@@ -9252,16 +9255,16 @@
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>177</v>
+        <v>670</v>
       </c>
       <c r="B342" t="s">
-        <v>719</v>
+        <v>671</v>
       </c>
       <c r="C342" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D342" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E342" t="s">
         <v>5</v>
@@ -9271,13 +9274,13 @@
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>720</v>
+        <v>672</v>
       </c>
       <c r="B343" t="s">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="C343" t="s">
-        <v>255</v>
+        <v>469</v>
       </c>
       <c r="D343" t="s">
         <v>6</v>
@@ -9290,10 +9293,10 @@
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>722</v>
+        <v>676</v>
       </c>
       <c r="B344" t="s">
-        <v>723</v>
+        <v>677</v>
       </c>
       <c r="C344" t="s">
         <v>255</v>
@@ -9309,16 +9312,16 @@
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>21</v>
+        <v>678</v>
       </c>
       <c r="B345" t="s">
-        <v>724</v>
+        <v>679</v>
       </c>
       <c r="C345" t="s">
-        <v>257</v>
+        <v>469</v>
       </c>
       <c r="D345" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E345" t="s">
         <v>5</v>
@@ -9328,16 +9331,16 @@
     </row>
     <row r="346" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="B346" t="s">
-        <v>725</v>
+        <v>681</v>
       </c>
       <c r="C346" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D346" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E346" t="s">
         <v>5</v>
@@ -9347,16 +9350,16 @@
     </row>
     <row r="347" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>116</v>
+        <v>682</v>
       </c>
       <c r="B347" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="C347" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D347" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E347" t="s">
         <v>5</v>
@@ -9366,16 +9369,16 @@
     </row>
     <row r="348" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>727</v>
+        <v>692</v>
       </c>
       <c r="C348" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D348" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E348" t="s">
         <v>5</v>
@@ -9385,13 +9388,13 @@
     </row>
     <row r="349" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>728</v>
+        <v>53</v>
       </c>
       <c r="B349" t="s">
-        <v>729</v>
+        <v>694</v>
       </c>
       <c r="C349" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D349" t="s">
         <v>6</v>
@@ -9404,13 +9407,13 @@
     </row>
     <row r="350" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>730</v>
+        <v>78</v>
       </c>
       <c r="B350" t="s">
-        <v>731</v>
+        <v>695</v>
       </c>
       <c r="C350" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D350" t="s">
         <v>6</v>
@@ -9423,13 +9426,13 @@
     </row>
     <row r="351" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>732</v>
+        <v>103</v>
       </c>
       <c r="B351" t="s">
-        <v>733</v>
+        <v>696</v>
       </c>
       <c r="C351" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="D351" t="s">
         <v>6</v>
@@ -9442,13 +9445,13 @@
     </row>
     <row r="352" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>734</v>
+        <v>100</v>
       </c>
       <c r="B352" t="s">
-        <v>735</v>
+        <v>697</v>
       </c>
       <c r="C352" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D352" t="s">
         <v>6</v>
@@ -9461,10 +9464,10 @@
     </row>
     <row r="353" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>84</v>
+        <v>698</v>
       </c>
       <c r="B353" t="s">
-        <v>736</v>
+        <v>699</v>
       </c>
       <c r="C353" t="s">
         <v>255</v>
@@ -9480,13 +9483,13 @@
     </row>
     <row r="354" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="B354" t="s">
-        <v>737</v>
+        <v>700</v>
       </c>
       <c r="C354" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D354" t="s">
         <v>6</v>
@@ -9499,13 +9502,13 @@
     </row>
     <row r="355" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>148</v>
+        <v>701</v>
       </c>
       <c r="B355" t="s">
-        <v>738</v>
+        <v>702</v>
       </c>
       <c r="C355" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D355" t="s">
         <v>6</v>
@@ -9518,13 +9521,13 @@
     </row>
     <row r="356" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="B356" t="s">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="C356" t="s">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D356" t="s">
         <v>6</v>
@@ -9537,13 +9540,13 @@
     </row>
     <row r="357" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>741</v>
+        <v>705</v>
       </c>
       <c r="B357" t="s">
-        <v>742</v>
+        <v>706</v>
       </c>
       <c r="C357" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D357" t="s">
         <v>6</v>
@@ -9556,13 +9559,13 @@
     </row>
     <row r="358" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>743</v>
+        <v>707</v>
       </c>
       <c r="B358" t="s">
-        <v>744</v>
+        <v>708</v>
       </c>
       <c r="C358" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="D358" t="s">
         <v>6</v>
@@ -9575,13 +9578,13 @@
     </row>
     <row r="359" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>745</v>
+        <v>709</v>
       </c>
       <c r="B359" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
       <c r="C359" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D359" t="s">
         <v>6</v>
@@ -9594,13 +9597,13 @@
     </row>
     <row r="360" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>747</v>
+        <v>711</v>
       </c>
       <c r="B360" t="s">
-        <v>748</v>
+        <v>712</v>
       </c>
       <c r="C360" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D360" t="s">
         <v>6</v>
@@ -9613,10 +9616,10 @@
     </row>
     <row r="361" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>204</v>
+        <v>713</v>
       </c>
       <c r="B361" t="s">
-        <v>749</v>
+        <v>714</v>
       </c>
       <c r="C361" t="s">
         <v>259</v>
@@ -9632,10 +9635,10 @@
     </row>
     <row r="362" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>750</v>
+        <v>716</v>
       </c>
       <c r="B362" t="s">
-        <v>751</v>
+        <v>717</v>
       </c>
       <c r="C362" t="s">
         <v>255</v>
@@ -9651,16 +9654,16 @@
     </row>
     <row r="363" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>163</v>
+        <v>720</v>
       </c>
       <c r="B363" t="s">
-        <v>752</v>
+        <v>721</v>
       </c>
       <c r="C363" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D363" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
         <v>5</v>
@@ -9670,10 +9673,10 @@
     </row>
     <row r="364" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>780</v>
+        <v>722</v>
       </c>
       <c r="B364" t="s">
-        <v>753</v>
+        <v>723</v>
       </c>
       <c r="C364" t="s">
         <v>255</v>
@@ -9689,16 +9692,16 @@
     </row>
     <row r="365" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>754</v>
+        <v>728</v>
       </c>
       <c r="B365" t="s">
-        <v>755</v>
+        <v>729</v>
       </c>
       <c r="C365" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D365" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
         <v>5</v>
@@ -9708,16 +9711,16 @@
     </row>
     <row r="366" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>110</v>
+        <v>730</v>
       </c>
       <c r="B366" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
       <c r="C366" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D366" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
         <v>5</v>
@@ -9727,16 +9730,16 @@
     </row>
     <row r="367" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="B367" t="s">
-        <v>758</v>
+        <v>733</v>
       </c>
       <c r="C367" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="D367" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E367" t="s">
         <v>5</v>
@@ -9746,16 +9749,16 @@
     </row>
     <row r="368" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>759</v>
+        <v>734</v>
       </c>
       <c r="B368" t="s">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="C368" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D368" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E368" t="s">
         <v>5</v>
@@ -9765,16 +9768,16 @@
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>761</v>
+        <v>84</v>
       </c>
       <c r="B369" t="s">
-        <v>762</v>
+        <v>736</v>
       </c>
       <c r="C369" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D369" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E369" t="s">
         <v>5</v>
@@ -9784,16 +9787,16 @@
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>763</v>
+        <v>135</v>
       </c>
       <c r="B370" t="s">
-        <v>764</v>
+        <v>737</v>
       </c>
       <c r="C370" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D370" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E370" t="s">
         <v>5</v>
@@ -9803,16 +9806,16 @@
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B371" t="s">
-        <v>765</v>
+        <v>738</v>
       </c>
       <c r="C371" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D371" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
         <v>5</v>
@@ -9822,16 +9825,16 @@
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>114</v>
+        <v>739</v>
       </c>
       <c r="B372" t="s">
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="C372" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="D372" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E372" t="s">
         <v>5</v>
@@ -9841,16 +9844,16 @@
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>159</v>
+        <v>741</v>
       </c>
       <c r="B373" t="s">
-        <v>767</v>
+        <v>742</v>
       </c>
       <c r="C373" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D373" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E373" t="s">
         <v>5</v>
@@ -9860,16 +9863,16 @@
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>127</v>
+        <v>743</v>
       </c>
       <c r="B374" t="s">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="C374" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="D374" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
         <v>5</v>
@@ -9879,16 +9882,16 @@
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>769</v>
+        <v>745</v>
       </c>
       <c r="B375" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="C375" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D375" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E375" t="s">
         <v>5</v>
@@ -9898,16 +9901,16 @@
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>95</v>
+        <v>747</v>
       </c>
       <c r="B376" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="C376" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D376" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E376" t="s">
         <v>5</v>
@@ -9917,16 +9920,16 @@
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B377" t="s">
-        <v>772</v>
+        <v>749</v>
       </c>
       <c r="C377" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D377" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E377" t="s">
         <v>5</v>
@@ -9936,10 +9939,10 @@
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>105</v>
+        <v>750</v>
       </c>
       <c r="B378" t="s">
-        <v>773</v>
+        <v>751</v>
       </c>
       <c r="C378" t="s">
         <v>255</v>
@@ -9955,10 +9958,10 @@
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="B379" t="s">
-        <v>775</v>
+        <v>753</v>
       </c>
       <c r="C379" t="s">
         <v>255</v>
@@ -9974,16 +9977,16 @@
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="B380" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C380" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="D380" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E380" t="s">
         <v>5</v>
@@ -9993,16 +9996,16 @@
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B381" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C381" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D381" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E381" t="s">
         <v>5</v>
@@ -10030,6 +10033,11 @@
       <c r="W382" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W382" xr:uid="{3EFBEEA5-2CEF-42F0-81B3-480430634EDF}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W382">
+      <sortCondition ref="D1:D382"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
